--- a/web/files/九龙-红磡-瑅海.xlsx
+++ b/web/files/九龙-红磡-瑅海.xlsx
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4267,34 +4267,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H53" s="5" t="n">
+        <v>9220000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>23948</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>7837000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>20356</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4329,7 +4321,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4337,34 +4329,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H54" s="5" t="n">
+        <v>9293000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>24391</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>7899050</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>20732</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4399,7 +4383,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4407,34 +4391,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H55" s="5" t="n">
+        <v>9343000</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>24522</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>7941550</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>20844</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -4959,7 +4935,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4967,34 +4943,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H63" s="5" t="n">
+        <v>9183000</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>23852</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>7805550</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>20274</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -5029,7 +4997,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5037,34 +5005,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H64" s="5" t="n">
+        <v>9256000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>24294</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>7867600</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>20650</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -5099,7 +5059,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -5107,34 +5067,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H65" s="5" t="n">
+        <v>9306000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>24425</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>7910100</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>20761</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -5659,7 +5611,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5667,34 +5619,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>9111000</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>23665</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>7744350</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>20115</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -5729,7 +5673,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5737,34 +5681,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H74" s="5" t="n">
+        <v>9183000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>24102</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>7805550</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>20487</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5799,7 +5735,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5807,34 +5743,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H75" s="5" t="n">
+        <v>9232000</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>24231</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>7847200</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>20596</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -6359,7 +6287,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6367,34 +6295,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H83" s="5" t="n">
+        <v>9039000</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>23478</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>7683150</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>19956</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -6429,7 +6349,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6437,34 +6357,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>9111000</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>23913</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>7744350</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>20326</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -6499,7 +6411,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6507,34 +6419,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H85" s="5" t="n">
+        <v>9159000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>24039</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>7785150</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>20433</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -7059,7 +6963,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -7067,34 +6971,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H93" s="5" t="n">
+        <v>8967000</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>23291</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>7621950</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>19797</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -7129,7 +7025,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -7137,34 +7033,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H94" s="5" t="n">
+        <v>9039000</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>23724</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>7683150</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>20166</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
@@ -7199,7 +7087,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -7207,34 +7095,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H95" s="5" t="n">
+        <v>9086000</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>23848</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>7723100</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>20271</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -8209,7 +8089,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -8217,34 +8097,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H110" s="5" t="n">
+        <v>7691000</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>22687</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>6537350</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>19284</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -8861,7 +8733,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -8869,34 +8741,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H120" s="5" t="n">
+        <v>7576000</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>22348</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>6439600</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>18996</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N120" s="3" t="inlineStr">
@@ -9513,7 +9377,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9521,34 +9385,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H130" s="5" t="n">
+        <v>7465000</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>22021</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>6345250</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>18718</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N130" s="3" t="inlineStr">
@@ -10165,7 +10021,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -10173,34 +10029,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H140" s="5" t="n">
+        <v>7354000</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>21693</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>6250900</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>18439</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
@@ -10817,7 +10665,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -10825,34 +10673,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H150" s="5" t="n">
+        <v>7286000</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>21493</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>6193100</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>18269</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -11469,7 +11309,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -11477,34 +11317,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H160" s="5" t="n">
+        <v>7214000</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>21280</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>6131900</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>18088</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -12121,7 +11953,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -12129,34 +11961,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H170" s="5" t="n">
+        <v>7178000</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>21174</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L170" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>6101300</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>17998</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N170" s="3" t="inlineStr">
@@ -17413,7 +17237,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -17421,34 +17245,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H248" s="5" t="n">
+        <v>9293000</v>
+      </c>
+      <c r="I248" s="5" t="n">
+        <v>24138</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L248" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>7899050</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>20517</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -18183,7 +17999,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -18191,34 +18007,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H259" s="5" t="n">
+        <v>9257000</v>
+      </c>
+      <c r="I259" s="5" t="n">
+        <v>24044</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L259" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>7868450</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>20438</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
@@ -18953,7 +18761,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -18961,34 +18769,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H270" s="5" t="n">
+        <v>9220000</v>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>23948</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L270" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>7837000</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>20356</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
@@ -19723,7 +19523,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -19731,34 +19531,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H281" s="5" t="n">
+        <v>9184000</v>
+      </c>
+      <c r="I281" s="5" t="n">
+        <v>23855</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L281" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>7806400</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>20276</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
@@ -20493,7 +20285,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -20501,34 +20293,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H292" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I292" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H292" s="5" t="n">
+        <v>9111000</v>
+      </c>
+      <c r="I292" s="5" t="n">
+        <v>23665</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K292" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L292" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K292" s="5" t="n">
+        <v>7744350</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>20115</v>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N292" s="3" t="inlineStr">
@@ -21263,7 +21047,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -21271,34 +21055,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H303" s="5" t="n">
+        <v>9039000</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>23478</v>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L303" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K303" s="5" t="n">
+        <v>7683150</v>
+      </c>
+      <c r="L303" s="5" t="n">
+        <v>19956</v>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N303" s="3" t="inlineStr">
@@ -21823,7 +21599,7 @@
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -21831,34 +21607,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H311" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I311" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H311" s="5" t="n">
+        <v>8702000</v>
+      </c>
+      <c r="I311" s="5" t="n">
+        <v>22661</v>
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K311" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L311" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K311" s="5" t="n">
+        <v>7396700</v>
+      </c>
+      <c r="L311" s="5" t="n">
+        <v>19262</v>
       </c>
       <c r="M311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N311" s="3" t="inlineStr">
@@ -21893,7 +21661,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -21901,34 +21669,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H312" s="5" t="n">
+        <v>8661000</v>
+      </c>
+      <c r="I312" s="5" t="n">
+        <v>22555</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L312" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K312" s="5" t="n">
+        <v>7361850</v>
+      </c>
+      <c r="L312" s="5" t="n">
+        <v>19171</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N312" s="3" t="inlineStr">
@@ -22033,7 +21793,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -22041,34 +21801,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H314" s="5" t="n">
+        <v>8967000</v>
+      </c>
+      <c r="I314" s="5" t="n">
+        <v>23291</v>
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L314" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K314" s="5" t="n">
+        <v>7621950</v>
+      </c>
+      <c r="L314" s="5" t="n">
+        <v>19797</v>
       </c>
       <c r="M314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N314" s="3" t="inlineStr">
@@ -22243,7 +21995,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -22251,34 +22003,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H317" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I317" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H317" s="5" t="n">
+        <v>11261000</v>
+      </c>
+      <c r="I317" s="5" t="n">
+        <v>24695</v>
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K317" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L317" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K317" s="5" t="n">
+        <v>9571850</v>
+      </c>
+      <c r="L317" s="5" t="n">
+        <v>20991</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -22593,7 +22337,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -22601,34 +22345,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H322" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I322" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H322" s="5" t="n">
+        <v>8574000</v>
+      </c>
+      <c r="I322" s="5" t="n">
+        <v>22328</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K322" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L322" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K322" s="5" t="n">
+        <v>7287900</v>
+      </c>
+      <c r="L322" s="5" t="n">
+        <v>18979</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N322" s="3" t="inlineStr">
@@ -22663,7 +22399,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -22671,34 +22407,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H323" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I323" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H323" s="5" t="n">
+        <v>8533000</v>
+      </c>
+      <c r="I323" s="5" t="n">
+        <v>22221</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K323" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L323" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K323" s="5" t="n">
+        <v>7253050</v>
+      </c>
+      <c r="L323" s="5" t="n">
+        <v>18888</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N323" s="3" t="inlineStr">
@@ -22803,7 +22531,7 @@
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -22811,34 +22539,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H325" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I325" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H325" s="5" t="n">
+        <v>8897000</v>
+      </c>
+      <c r="I325" s="5" t="n">
+        <v>23109</v>
       </c>
       <c r="J325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K325" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L325" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K325" s="5" t="n">
+        <v>7562450</v>
+      </c>
+      <c r="L325" s="5" t="n">
+        <v>19643</v>
       </c>
       <c r="M325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N325" s="3" t="inlineStr">
@@ -23013,7 +22733,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -23021,34 +22741,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H328" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I328" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H328" s="5" t="n">
+        <v>11161000</v>
+      </c>
+      <c r="I328" s="5" t="n">
+        <v>24476</v>
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K328" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L328" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K328" s="5" t="n">
+        <v>9486850</v>
+      </c>
+      <c r="L328" s="5" t="n">
+        <v>20804</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N328" s="3" t="inlineStr">
@@ -23557,7 +23269,7 @@
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -23565,34 +23277,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H336" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I336" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H336" s="5" t="n">
+        <v>8826000</v>
+      </c>
+      <c r="I336" s="5" t="n">
+        <v>22925</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K336" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L336" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K336" s="5" t="n">
+        <v>7502100</v>
+      </c>
+      <c r="L336" s="5" t="n">
+        <v>19486</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金付款計劃</t>
         </is>
       </c>
       <c r="N336" s="3" t="inlineStr">
@@ -23767,7 +23471,7 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -23775,34 +23479,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H339" s="5" t="n">
+        <v>11061000</v>
+      </c>
+      <c r="I339" s="5" t="n">
+        <v>24257</v>
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L339" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K339" s="5" t="n">
+        <v>9401850</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>20618</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N339" s="3" t="inlineStr">
@@ -24513,7 +24209,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -24521,34 +24217,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H350" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I350" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H350" s="5" t="n">
+        <v>10952000</v>
+      </c>
+      <c r="I350" s="5" t="n">
+        <v>24018</v>
       </c>
       <c r="J350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K350" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L350" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K350" s="5" t="n">
+        <v>9309200</v>
+      </c>
+      <c r="L350" s="5" t="n">
+        <v>20415</v>
       </c>
       <c r="M350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N350" s="3" t="inlineStr">
@@ -25259,7 +24947,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -25267,34 +24955,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H361" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I361" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H361" s="5" t="n">
+        <v>10843000</v>
+      </c>
+      <c r="I361" s="5" t="n">
+        <v>23779</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K361" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L361" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K361" s="5" t="n">
+        <v>9216550</v>
+      </c>
+      <c r="L361" s="5" t="n">
+        <v>20212</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N361" s="3" t="inlineStr">
@@ -26005,7 +25685,7 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -26013,34 +25693,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H372" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I372" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H372" s="5" t="n">
+        <v>10736000</v>
+      </c>
+      <c r="I372" s="5" t="n">
+        <v>23544</v>
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K372" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L372" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K372" s="5" t="n">
+        <v>9125600</v>
+      </c>
+      <c r="L372" s="5" t="n">
+        <v>20012</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N372" s="3" t="inlineStr">
@@ -26751,7 +26423,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -26759,34 +26431,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H383" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I383" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H383" s="5" t="n">
+        <v>10631000</v>
+      </c>
+      <c r="I383" s="5" t="n">
+        <v>23314</v>
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K383" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L383" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K383" s="5" t="n">
+        <v>9036350</v>
+      </c>
+      <c r="L383" s="5" t="n">
+        <v>19817</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N383" s="3" t="inlineStr">
@@ -27497,7 +27161,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -27505,34 +27169,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H394" s="5" t="n">
+        <v>10526000</v>
+      </c>
+      <c r="I394" s="5" t="n">
+        <v>23083</v>
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L394" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K394" s="5" t="n">
+        <v>8947100</v>
+      </c>
+      <c r="L394" s="5" t="n">
+        <v>19621</v>
       </c>
       <c r="M394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N394" s="3" t="inlineStr">
@@ -28243,7 +27899,7 @@
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G405" s="3" t="inlineStr">
@@ -28251,34 +27907,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H405" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I405" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H405" s="5" t="n">
+        <v>10453000</v>
+      </c>
+      <c r="I405" s="5" t="n">
+        <v>22923</v>
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K405" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L405" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K405" s="5" t="n">
+        <v>8885050</v>
+      </c>
+      <c r="L405" s="5" t="n">
+        <v>19485</v>
       </c>
       <c r="M405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N405" s="3" t="inlineStr">
@@ -28989,7 +28637,7 @@
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
@@ -28997,34 +28645,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H416" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I416" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H416" s="5" t="n">
+        <v>10380000</v>
+      </c>
+      <c r="I416" s="5" t="n">
+        <v>22763</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K416" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L416" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K416" s="5" t="n">
+        <v>8823000</v>
+      </c>
+      <c r="L416" s="5" t="n">
+        <v>19349</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N416" s="3" t="inlineStr">
@@ -29735,7 +29375,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -29743,34 +29383,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H427" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I427" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H427" s="5" t="n">
+        <v>10308000</v>
+      </c>
+      <c r="I427" s="5" t="n">
+        <v>22605</v>
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K427" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L427" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K427" s="5" t="n">
+        <v>8761800</v>
+      </c>
+      <c r="L427" s="5" t="n">
+        <v>19214</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N427" s="3" t="inlineStr">
@@ -30481,7 +30113,7 @@
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
@@ -30489,34 +30121,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H438" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I438" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H438" s="5" t="n">
+        <v>10237000</v>
+      </c>
+      <c r="I438" s="5" t="n">
+        <v>22450</v>
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K438" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L438" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K438" s="5" t="n">
+        <v>8701450</v>
+      </c>
+      <c r="L438" s="5" t="n">
+        <v>19082</v>
       </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>輕鬆120天現金付款計劃</t>
         </is>
       </c>
       <c r="N438" s="3" t="inlineStr">
@@ -31658,7 +31282,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -31673,7 +31297,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>125</t>
         </is>
       </c>
     </row>
@@ -32186,28 +31810,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>B2 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
+$934万
+$24,522/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>B3 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
+$929万
+$24,391/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$922万
+$23,948/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -32273,28 +31897,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>B2 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
+$931万
+$24,425/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>B3 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
+$926万
+$24,294/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$918万
+$23,852/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -32360,28 +31984,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>B2 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
+$923万
+$24,231/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>B3 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
+$918万
+$24,102/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$911万
+$23,665/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -32447,28 +32071,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>B2 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
+$916万
+$24,039/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>B3 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
+$911万
+$23,913/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$904万
+$23,478/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -32534,28 +32158,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>B2 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
+$909万
+$23,848/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>B3 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
+$904万
+$23,724/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$897万
+$23,291/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -32748,12 +32372,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K16" s="20" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>C3 | 339呎 (1房)
--
--
-(待售)</t>
+$769万
+$22,687/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32835,12 +32459,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K17" s="20" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>C3 | 339呎 (1房)
--
--
-(待售)</t>
+$758万
+$22,348/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -32922,12 +32546,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>C3 | 339呎 (1房)
--
--
-(待售)</t>
+$746万
+$22,021/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33009,12 +32633,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K19" s="20" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>C3 | 339呎 (1房)
--
--
-(待售)</t>
+$735万
+$21,693/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33096,12 +32720,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K20" s="20" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>C3 | 339呎 (1房)
--
--
-(待售)</t>
+$729万
+$21,493/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33183,12 +32807,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K21" s="20" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>C3 | 339呎 (1房)
--
--
-(待售)</t>
+$721万
+$21,280/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33270,12 +32894,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K22" s="20" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>C3 | 339呎 (1房)
--
--
-(待售)</t>
+$718万
+$21,174/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -33655,7 +33279,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -33670,7 +33294,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -34083,12 +33707,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$929万
+$24,138/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -34178,12 +33802,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$926万
+$24,044/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -34273,12 +33897,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$922万
+$23,948/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -34368,12 +33992,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$918万
+$23,855/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -34463,12 +34087,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$911万
+$23,665/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -34558,12 +34182,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$904万
+$23,478/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -34629,60 +34253,60 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
+$1126万
+$24,695/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 381呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>B2 | 381呎 (2房)
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 381呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>B3 | 381呎 (2房)
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 385呎 (2房)
+$897万
+$23,291/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 460呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>C1 | 460呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>C2 | 384呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
+$866万
+$22,555/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>C3 | 384呎 (2房)
--
--
-(待售)</t>
+$870万
+$22,661/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34724,60 +34348,60 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
+$1116万
+$24,476/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 381呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>B2 | 381呎 (2房)
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 381呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>B3 | 381呎 (2房)
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 385呎 (2房)
+$890万
+$23,109/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 460呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>C1 | 460呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="20" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>C2 | 384呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
+$853万
+$22,221/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>C3 | 384呎 (2房)
--
--
-(待售)</t>
+$857万
+$22,328/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -34819,36 +34443,36 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
+$1106万
+$24,257/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 381呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>B2 | 381呎 (2房)
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 381呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>B3 | 381呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>B5 | 385呎 (2房)
--
--
-(待售)</t>
+$883万
+$22,925/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -34914,12 +34538,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1095万
+$24,018/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -35009,12 +34633,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1084万
+$23,779/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -35104,12 +34728,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1074万
+$23,544/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -35199,12 +34823,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1063万
+$23,314/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -35294,12 +34918,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1053万
+$23,083/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -35389,12 +35013,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1045万
+$22,923/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -35484,12 +35108,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1038万
+$22,763/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -35579,12 +35203,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1031万
+$22,605/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -35674,12 +35298,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>B1 | 456呎 (2房)
--
--
-(待售)</t>
+$1024万
+$22,450/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
